--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484815_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484815_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5936</v>
+        <v>1.6911</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0275</v>
+        <v>1.125</v>
       </c>
       <c r="F2" t="n">
         <v>0.5661</v>
@@ -610,10 +610,10 @@
         <v>0.5661</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0588</v>
+        <v>0.0386</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0588</v>
+        <v>0.0386</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GARCIA NAVEA</t>
+          <t>C. GILABERT FERRI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9344</v>
+        <v>1.1995</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0593</v>
+        <v>1.3656</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.125</v>
+        <v>-0.1661</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3794</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0063</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3857</v>
+        <v>-0.002</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1237</v>
+        <v>0.0834</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1239</v>
+        <v>0.0423</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9998</v>
+        <v>0.0411</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7443</v>
+        <v>-0.7099</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1302</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3859</v>
+        <v>-0.0431</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0757</v>
+        <v>0.1887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.9062</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8305</v>
+        <v>0.1887</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4984</v>
+        <v>0.3921</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5966</v>
+        <v>0.037</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9019</v>
+        <v>0.3551</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8678</v>
+        <v>1.2452</v>
       </c>
       <c r="W4" t="n">
         <v>1.2452</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.4577</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2562</v>
+        <v>0.9639</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4533</v>
+        <v>-0.5062</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1764</v>
@@ -844,13 +844,13 @@
         <v>0.5661</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4133</v>
+        <v>0.068</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4144</v>
+        <v>0.1221</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0541</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. GILABERT FERRI</t>
+          <t>J. GARCIA NAVEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6716</v>
+        <v>0.2356</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9171</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2455</v>
+        <v>-0.3366</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6264999999999999</v>
+        <v>3.3794</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.0063</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.002</v>
+        <v>3.3857</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0834</v>
+        <v>4.1237</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0423</v>
+        <v>2.1239</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0411</v>
+        <v>1.9998</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7099</v>
+        <v>-0.7443</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-2.1302</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0431</v>
+        <v>1.3859</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.9062</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1887</v>
+        <v>2.8305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1358</v>
+        <v>0.7996</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4115</v>
+        <v>0.1094</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2757</v>
+        <v>0.6902</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2452</v>
+        <v>-1.8678</v>
       </c>
       <c r="W6" t="n">
         <v>1.2452</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NUNEZ NIEVAS</t>
+          <t>G. GARCIA CARCASES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3768</v>
+        <v>0.1951</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.261</v>
+        <v>-0.2667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8842</v>
+        <v>0.4618</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9206</v>
+        <v>-1.3249</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.949</v>
+        <v>-0.3287</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0284</v>
+        <v>-0.9962</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2723</v>
+        <v>-0.0237</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7374</v>
+        <v>1.1676</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4651</v>
+        <v>-1.1913</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6483</v>
+        <v>-1.3012</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.2116</v>
+        <v>-1.4963</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5633</v>
+        <v>0.1951</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8305</v>
+        <v>-1.1322</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6418</v>
+        <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4873</v>
+        <v>-0.1972</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5966</v>
+        <v>-0.356</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1093</v>
+        <v>0.1588</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2452</v>
+        <v>0.9624</v>
       </c>
       <c r="W7" t="n">
         <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2828</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>J. NUNEZ NIEVAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3882</v>
+        <v>-0.2316</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4314</v>
+        <v>-1.5919</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8195</v>
+        <v>1.3604</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1742</v>
+        <v>-1.9206</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2238</v>
+        <v>-3.949</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0496</v>
+        <v>2.0284</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1362</v>
+        <v>-0.2723</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6624</v>
+        <v>-1.7374</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5262</v>
+        <v>1.4651</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.962</v>
+        <v>-1.6483</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.4386</v>
+        <v>-2.2116</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4765</v>
+        <v>0.5633</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.887</v>
+        <v>2.6418</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3621</v>
+        <v>0.6325</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1822</v>
+        <v>0.2656</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1799</v>
+        <v>0.3669</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9244</v>
+        <v>1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GARCIA CARCASES</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5218</v>
+        <v>-0.6397</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8512999999999999</v>
+        <v>0.1004</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3295</v>
+        <v>-0.7402</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3249</v>
+        <v>0.1742</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3287</v>
+        <v>0.2238</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9962</v>
+        <v>-0.0496</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0237</v>
+        <v>2.1362</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1676</v>
+        <v>2.6624</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1913</v>
+        <v>-0.5262</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3012</v>
+        <v>-1.962</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4963</v>
+        <v>-2.4386</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1951</v>
+        <v>0.4765</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
         <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9141</v>
+        <v>0.1105</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9406</v>
+        <v>-0.1488</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0265</v>
+        <v>0.2593</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9624</v>
+        <v>-0.9244</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2828</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9396</v>
+        <v>-0.6846</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4544</v>
+        <v>0.0915</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4852</v>
+        <v>-0.7762</v>
       </c>
       <c r="G10" t="n">
         <v>-4.407</v>
@@ -1234,13 +1234,13 @@
         <v>2.6418</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7125</v>
+        <v>0.9674</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4674</v>
+        <v>0.0786</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1799</v>
+        <v>0.8889</v>
       </c>
       <c r="V10" t="n">
         <v>0.3018</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5616</v>
+        <v>-1.3668</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8259</v>
+        <v>-0.6311</v>
       </c>
       <c r="F11" t="n">
         <v>-0.7357</v>
@@ -1312,10 +1312,10 @@
         <v>0.1887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3063</v>
+        <v>-0.1114</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1764</v>
+        <v>0.0185</v>
       </c>
       <c r="U11" t="n">
         <v>-0.1299</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.698</v>
+        <v>-1.6715</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6872</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0108</v>
+        <v>-0.9843</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9211</v>
@@ -1390,13 +1390,13 @@
         <v>0.1887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0412</v>
+        <v>-0.0147</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9244</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1339</v>
+        <v>-2.508</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6014</v>
+        <v>-1.7374</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5325</v>
+        <v>-0.7706</v>
       </c>
       <c r="G13" t="n">
         <v>-4.1241</v>
@@ -1468,13 +1468,13 @@
         <v>3.3966</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2921</v>
+        <v>0.9179</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2438</v>
+        <v>0.1078</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0482</v>
+        <v>0.8102</v>
       </c>
       <c r="V13" t="n">
         <v>0.3208</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.0665</v>
+        <v>-1.7723</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5612000000000004</v>
+        <v>0.8551000000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6277</v>
+        <v>-2.6276</v>
       </c>
       <c r="G14" t="n">
         <v>-8.263300000000001</v>
@@ -1516,7 +1516,7 @@
         <v>-12.5921</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3285</v>
+        <v>4.328499999999999</v>
       </c>
       <c r="J14" t="n">
         <v>5.775300000000001</v>
@@ -1546,16 +1546,16 @@
         <v>16.983</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3095</v>
+        <v>3.6033</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.07989999999999978</v>
+        <v>0.214</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3893</v>
+        <v>3.3895</v>
       </c>
       <c r="V14" t="n">
-        <v>0.05700000000000049</v>
+        <v>0.05700000000000027</v>
       </c>
       <c r="W14" t="n">
         <v>9.0182</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0828</v>
+        <v>6.2428</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7336</v>
+        <v>3.0259</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3492</v>
+        <v>3.2169</v>
       </c>
       <c r="G15" t="n">
         <v>4.3081</v>
@@ -1624,13 +1624,13 @@
         <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0388</v>
+        <v>0.1989</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.458</v>
+        <v>-0.1657</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4968</v>
+        <v>0.3645</v>
       </c>
       <c r="V15" t="n">
         <v>0.6036</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9494</v>
+        <v>4.2409</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5129</v>
+        <v>4.8309</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5636</v>
+        <v>-0.59</v>
       </c>
       <c r="G16" t="n">
         <v>4.7387</v>
@@ -1702,13 +1702,13 @@
         <v>2.4531</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1475</v>
+        <v>-0.856</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1945</v>
+        <v>-0.4875</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.342</v>
+        <v>-0.3685</v>
       </c>
       <c r="V16" t="n">
         <v>1.8678</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.201</v>
+        <v>2.2707</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.401</v>
+        <v>-0.5959</v>
       </c>
       <c r="F17" t="n">
-        <v>2.602</v>
+        <v>2.8665</v>
       </c>
       <c r="G17" t="n">
         <v>0.2664</v>
@@ -1780,13 +1780,13 @@
         <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3309</v>
+        <v>0.4006</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2504</v>
+        <v>0.0555</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0806</v>
+        <v>0.3451</v>
       </c>
       <c r="V17" t="n">
         <v>1.2262</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. MARTINEZ BERTOMEU</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9202</v>
+        <v>1.0297</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7528</v>
+        <v>-0.8335</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1674</v>
+        <v>1.8632</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9888</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9908</v>
+        <v>0.1002</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.002</v>
+        <v>-0.632</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0976</v>
+        <v>-0.3028</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0565</v>
+        <v>0.9141</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0411</v>
+        <v>-1.2169</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1089</v>
+        <v>-0.229</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.8139</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0431</v>
+        <v>0.5849</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1957</v>
+        <v>-0.3255</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2968</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1011</v>
+        <v>0.2052</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>R. MARTINEZ BERTOMEU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7109</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1258</v>
+        <v>0.363</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8368</v>
+        <v>0.4055</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5318000000000001</v>
+        <v>0.9888</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1002</v>
+        <v>0.9908</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.632</v>
+        <v>-0.002</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3028</v>
+        <v>1.0976</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9141</v>
+        <v>1.0565</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2169</v>
+        <v>0.0411</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.229</v>
+        <v>-0.1089</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8139</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5849</v>
+        <v>-0.0431</v>
       </c>
       <c r="P19" t="n">
-        <v>1.887</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
-        <v>1.887</v>
+        <v>0.3774</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6443</v>
+        <v>0.0441</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.823</v>
+        <v>-0.0929</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1788</v>
+        <v>0.137</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9857</v>
+        <v>-1.0483</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6687</v>
+        <v>0.4738</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6544</v>
+        <v>-1.5222</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0376</v>
@@ -2014,13 +2014,13 @@
         <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7595</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3252</v>
+        <v>-0.52</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4344</v>
+        <v>-0.3021</v>
       </c>
       <c r="V20" t="n">
         <v>0.3018</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4545</v>
+        <v>-1.2068</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4685</v>
+        <v>0.6633</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.923</v>
+        <v>-1.8701</v>
       </c>
       <c r="G21" t="n">
         <v>0.3926</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9794</v>
+        <v>-0.7316</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7519</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2274</v>
+        <v>-0.1745</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2452</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6557</v>
+        <v>-2.6182</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5054</v>
+        <v>-3.0183</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8498</v>
+        <v>0.4</v>
       </c>
       <c r="G22" t="n">
         <v>0.8036</v>
@@ -2170,13 +2170,13 @@
         <v>2.6418</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5531</v>
+        <v>-0.5157</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2099</v>
+        <v>-0.7227</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.207</v>
       </c>
       <c r="V22" t="n">
         <v>1.2452</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.048</v>
+        <v>-3.0216</v>
       </c>
       <c r="E23" t="n">
         <v>-2.3391</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.709</v>
+        <v>-0.6825</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0634</v>
@@ -2248,13 +2248,13 @@
         <v>0.1887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2299</v>
+        <v>-0.2034</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6539</v>
+        <v>-4.5913</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1375</v>
+        <v>0.0573</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.5163</v>
+        <v>-4.6486</v>
       </c>
       <c r="G24" t="n">
         <v>1.3979</v>
@@ -2326,13 +2326,13 @@
         <v>0.9435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5614</v>
+        <v>-0.4988</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4456</v>
+        <v>-0.2508</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1158</v>
+        <v>-0.248</v>
       </c>
       <c r="V24" t="n">
         <v>-4.3582</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.0665</v>
+        <v>2.066499999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>2.627700000000002</v>
+        <v>2.627399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.561100000000001</v>
+        <v>-0.561300000000001</v>
       </c>
       <c r="G25" t="n">
         <v>8.263299999999999</v>
@@ -2392,10 +2392,10 @@
         <v>-4.1554</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.62</v>
+        <v>-1.619999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.830499999999999</v>
+        <v>-2.8305</v>
       </c>
       <c r="Q25" t="n">
         <v>-16.983</v>
@@ -2404,13 +2404,13 @@
         <v>14.1525</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.3097</v>
+        <v>-3.3095</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.3895</v>
+        <v>-3.3894</v>
       </c>
       <c r="U25" t="n">
-        <v>0.08000000000000003</v>
+        <v>0.07990000000000008</v>
       </c>
       <c r="V25" t="n">
         <v>-0.05700000000000038</v>
